--- a/12610764.xlsx
+++ b/12610764.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8133D04-0F85-4070-B22B-F52F3638D0A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C16CD0B1-D6E6-4122-9751-74AF75D75815}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="81">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2255,26 +2255,50 @@
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A32" s="13"/>
-      <c r="B32" s="14"/>
-      <c r="C32" s="14"/>
-      <c r="D32" s="14"/>
-      <c r="E32" s="14"/>
-      <c r="F32" s="14"/>
-      <c r="G32" s="14"/>
-      <c r="H32" s="14"/>
-      <c r="I32" s="15" t="str">
+      <c r="A32" s="13">
+        <v>46270</v>
+      </c>
+      <c r="B32" s="14">
+        <v>300</v>
+      </c>
+      <c r="C32" s="14">
+        <v>120</v>
+      </c>
+      <c r="D32" s="14">
+        <v>200</v>
+      </c>
+      <c r="E32" s="14">
+        <v>120</v>
+      </c>
+      <c r="F32" s="14">
+        <v>0</v>
+      </c>
+      <c r="G32" s="14">
+        <v>0</v>
+      </c>
+      <c r="H32" s="14">
+        <v>300</v>
+      </c>
+      <c r="I32" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J32" s="15" t="str">
+        <v>1040</v>
+      </c>
+      <c r="J32" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K32" s="16"/>
-      <c r="L32" s="16"/>
-      <c r="M32" s="16"/>
-      <c r="N32" s="17"/>
+        <v>400</v>
+      </c>
+      <c r="K32" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L32" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M32" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="N32" s="17" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A33" s="13"/>

--- a/12610764.xlsx
+++ b/12610764.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C16CD0B1-D6E6-4122-9751-74AF75D75815}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D821B926-15B3-4741-8FD7-5F5151DC204E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="81">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2301,26 +2301,50 @@
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A33" s="13"/>
-      <c r="B33" s="14"/>
-      <c r="C33" s="14"/>
-      <c r="D33" s="14"/>
-      <c r="E33" s="14"/>
-      <c r="F33" s="14"/>
-      <c r="G33" s="14"/>
-      <c r="H33" s="14"/>
-      <c r="I33" s="15" t="str">
+      <c r="A33" s="13">
+        <v>46271</v>
+      </c>
+      <c r="B33" s="14">
+        <v>250</v>
+      </c>
+      <c r="C33" s="14">
+        <v>120</v>
+      </c>
+      <c r="D33" s="14">
+        <v>200</v>
+      </c>
+      <c r="E33" s="14">
+        <v>120</v>
+      </c>
+      <c r="F33" s="14">
+        <v>0</v>
+      </c>
+      <c r="G33" s="14">
+        <v>0</v>
+      </c>
+      <c r="H33" s="14">
+        <v>200</v>
+      </c>
+      <c r="I33" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J33" s="15" t="str">
+        <v>890</v>
+      </c>
+      <c r="J33" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K33" s="16"/>
-      <c r="L33" s="16"/>
-      <c r="M33" s="16"/>
-      <c r="N33" s="17"/>
+        <v>550</v>
+      </c>
+      <c r="K33" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L33" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M33" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="N33" s="17" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A34" s="13"/>

--- a/12610764.xlsx
+++ b/12610764.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D821B926-15B3-4741-8FD7-5F5151DC204E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5409AFE3-CA6C-4282-BF6A-DBA32F68D1BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="82">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -278,6 +278,9 @@
   </si>
   <si>
     <t>Today is intractive session,it is very  helpful.</t>
+  </si>
+  <si>
+    <t>Enjoy in freshers party after over the class.</t>
   </si>
 </sst>
 </file>
@@ -2346,27 +2349,51 @@
         <v>71</v>
       </c>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A34" s="13"/>
-      <c r="B34" s="14"/>
-      <c r="C34" s="14"/>
-      <c r="D34" s="14"/>
-      <c r="E34" s="14"/>
-      <c r="F34" s="14"/>
-      <c r="G34" s="14"/>
-      <c r="H34" s="14"/>
-      <c r="I34" s="15" t="str">
+    <row r="34" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A34" s="13">
+        <v>46272</v>
+      </c>
+      <c r="B34" s="14">
+        <v>200</v>
+      </c>
+      <c r="C34" s="14">
+        <v>60</v>
+      </c>
+      <c r="D34" s="14">
+        <v>180</v>
+      </c>
+      <c r="E34" s="14">
+        <v>60</v>
+      </c>
+      <c r="F34" s="14">
+        <v>300</v>
+      </c>
+      <c r="G34" s="14">
+        <v>5</v>
+      </c>
+      <c r="H34" s="14">
+        <v>200</v>
+      </c>
+      <c r="I34" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J34" s="15" t="str">
+        <v>1000</v>
+      </c>
+      <c r="J34" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K34" s="16"/>
-      <c r="L34" s="16"/>
-      <c r="M34" s="16"/>
-      <c r="N34" s="17"/>
+        <v>440</v>
+      </c>
+      <c r="K34" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L34" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M34" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="N34" s="17" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A35" s="13"/>

--- a/12610764.xlsx
+++ b/12610764.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5409AFE3-CA6C-4282-BF6A-DBA32F68D1BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72A0EB4A-0591-401A-9F68-65B30C47522D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="83">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -281,6 +281,9 @@
   </si>
   <si>
     <t>Enjoy in freshers party after over the class.</t>
+  </si>
+  <si>
+    <t>Today is very happy.</t>
   </si>
 </sst>
 </file>
@@ -2396,26 +2399,50 @@
       </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A35" s="13"/>
-      <c r="B35" s="14"/>
-      <c r="C35" s="14"/>
-      <c r="D35" s="14"/>
-      <c r="E35" s="14"/>
-      <c r="F35" s="14"/>
-      <c r="G35" s="14"/>
-      <c r="H35" s="14"/>
-      <c r="I35" s="15" t="str">
+      <c r="A35" s="13">
+        <v>46273</v>
+      </c>
+      <c r="B35" s="14">
+        <v>200</v>
+      </c>
+      <c r="C35" s="14">
+        <v>120</v>
+      </c>
+      <c r="D35" s="14">
+        <v>200</v>
+      </c>
+      <c r="E35" s="14">
+        <v>60</v>
+      </c>
+      <c r="F35" s="14">
+        <v>350</v>
+      </c>
+      <c r="G35" s="14">
+        <v>7</v>
+      </c>
+      <c r="H35" s="14">
+        <v>200</v>
+      </c>
+      <c r="I35" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J35" s="15" t="str">
+        <v>1130</v>
+      </c>
+      <c r="J35" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K35" s="16"/>
-      <c r="L35" s="16"/>
-      <c r="M35" s="16"/>
-      <c r="N35" s="17"/>
+        <v>310</v>
+      </c>
+      <c r="K35" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L35" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M35" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="N35" s="17" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A36" s="13"/>

--- a/12610764.xlsx
+++ b/12610764.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72A0EB4A-0591-401A-9F68-65B30C47522D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D2A2171-775D-4D12-934E-2800795E8666}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="83">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2445,26 +2445,50 @@
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A36" s="13"/>
-      <c r="B36" s="14"/>
-      <c r="C36" s="14"/>
-      <c r="D36" s="14"/>
-      <c r="E36" s="14"/>
-      <c r="F36" s="14"/>
-      <c r="G36" s="14"/>
-      <c r="H36" s="14"/>
-      <c r="I36" s="15" t="str">
+      <c r="A36" s="13">
+        <v>46274</v>
+      </c>
+      <c r="B36" s="14">
+        <v>200</v>
+      </c>
+      <c r="C36" s="14">
+        <v>120</v>
+      </c>
+      <c r="D36" s="14">
+        <v>200</v>
+      </c>
+      <c r="E36" s="14">
+        <v>60</v>
+      </c>
+      <c r="F36" s="14">
+        <v>300</v>
+      </c>
+      <c r="G36" s="14">
+        <v>6</v>
+      </c>
+      <c r="H36" s="14">
+        <v>240</v>
+      </c>
+      <c r="I36" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J36" s="15" t="str">
+        <v>1120</v>
+      </c>
+      <c r="J36" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K36" s="16"/>
-      <c r="L36" s="16"/>
-      <c r="M36" s="16"/>
-      <c r="N36" s="17"/>
+        <v>320</v>
+      </c>
+      <c r="K36" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L36" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M36" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="N36" s="17" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A37" s="13"/>

--- a/12610764.xlsx
+++ b/12610764.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D2A2171-775D-4D12-934E-2800795E8666}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{852A9878-92E9-43BB-B621-F6580FCBD8DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="84">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -284,6 +284,9 @@
   </si>
   <si>
     <t>Today is very happy.</t>
+  </si>
+  <si>
+    <t>Today is  freshers party.I enjoy very hard.</t>
   </si>
 </sst>
 </file>
@@ -2490,27 +2493,51 @@
         <v>78</v>
       </c>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A37" s="13"/>
-      <c r="B37" s="14"/>
-      <c r="C37" s="14"/>
-      <c r="D37" s="14"/>
-      <c r="E37" s="14"/>
-      <c r="F37" s="14"/>
-      <c r="G37" s="14"/>
-      <c r="H37" s="14"/>
-      <c r="I37" s="15" t="str">
+    <row r="37" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A37" s="13">
+        <v>46275</v>
+      </c>
+      <c r="B37" s="14">
+        <v>200</v>
+      </c>
+      <c r="C37" s="14">
+        <v>120</v>
+      </c>
+      <c r="D37" s="14">
+        <v>100</v>
+      </c>
+      <c r="E37" s="14">
+        <v>30</v>
+      </c>
+      <c r="F37" s="14">
+        <v>150</v>
+      </c>
+      <c r="G37" s="14">
+        <v>3</v>
+      </c>
+      <c r="H37" s="14">
+        <v>200</v>
+      </c>
+      <c r="I37" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J37" s="15" t="str">
+        <v>800</v>
+      </c>
+      <c r="J37" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K37" s="16"/>
-      <c r="L37" s="16"/>
-      <c r="M37" s="16"/>
-      <c r="N37" s="17"/>
+        <v>640</v>
+      </c>
+      <c r="K37" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L37" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M37" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="N37" s="17" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A38" s="13"/>

--- a/12610764.xlsx
+++ b/12610764.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{852A9878-92E9-43BB-B621-F6580FCBD8DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{179B035C-F2A2-4D63-8CE7-3281AF0BAB67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="84">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2540,26 +2540,50 @@
       </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A38" s="13"/>
-      <c r="B38" s="14"/>
-      <c r="C38" s="14"/>
-      <c r="D38" s="14"/>
-      <c r="E38" s="14"/>
-      <c r="F38" s="14"/>
-      <c r="G38" s="14"/>
-      <c r="H38" s="14"/>
-      <c r="I38" s="15" t="str">
+      <c r="A38" s="13">
+        <v>46276</v>
+      </c>
+      <c r="B38" s="14">
+        <v>200</v>
+      </c>
+      <c r="C38" s="14">
+        <v>60</v>
+      </c>
+      <c r="D38" s="14">
+        <v>200</v>
+      </c>
+      <c r="E38" s="14">
+        <v>120</v>
+      </c>
+      <c r="F38" s="14">
+        <v>250</v>
+      </c>
+      <c r="G38" s="14">
+        <v>5</v>
+      </c>
+      <c r="H38" s="14">
+        <v>200</v>
+      </c>
+      <c r="I38" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J38" s="15" t="str">
+        <v>1030</v>
+      </c>
+      <c r="J38" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K38" s="16"/>
-      <c r="L38" s="16"/>
-      <c r="M38" s="16"/>
-      <c r="N38" s="17"/>
+        <v>410</v>
+      </c>
+      <c r="K38" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L38" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M38" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="N38" s="17" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A39" s="13"/>

--- a/12610764.xlsx
+++ b/12610764.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{179B035C-F2A2-4D63-8CE7-3281AF0BAB67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F93277E-D606-4C73-B7FD-1520AAD11DFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="85">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -287,6 +287,9 @@
   </si>
   <si>
     <t>Today is  freshers party.I enjoy very hard.</t>
+  </si>
+  <si>
+    <t>Very bad day.</t>
   </si>
 </sst>
 </file>
@@ -2586,26 +2589,50 @@
       </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A39" s="13"/>
-      <c r="B39" s="14"/>
-      <c r="C39" s="14"/>
-      <c r="D39" s="14"/>
-      <c r="E39" s="14"/>
-      <c r="F39" s="14"/>
-      <c r="G39" s="14"/>
-      <c r="H39" s="14"/>
-      <c r="I39" s="15" t="str">
+      <c r="A39" s="13">
+        <v>46277</v>
+      </c>
+      <c r="B39" s="14">
+        <v>250</v>
+      </c>
+      <c r="C39" s="14">
+        <v>120</v>
+      </c>
+      <c r="D39" s="14">
+        <v>200</v>
+      </c>
+      <c r="E39" s="14">
+        <v>120</v>
+      </c>
+      <c r="F39" s="14">
+        <v>0</v>
+      </c>
+      <c r="G39" s="14">
+        <v>0</v>
+      </c>
+      <c r="H39" s="14">
+        <v>300</v>
+      </c>
+      <c r="I39" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J39" s="15" t="str">
+        <v>990</v>
+      </c>
+      <c r="J39" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K39" s="16"/>
-      <c r="L39" s="16"/>
-      <c r="M39" s="16"/>
-      <c r="N39" s="17"/>
+        <v>450</v>
+      </c>
+      <c r="K39" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="L39" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="M39" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N39" s="17" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A40" s="13"/>
